--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
+          <t>Susanne Hernqvist, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -784,46 +784,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128832951</v>
+        <v>128832928</v>
       </c>
       <c r="B3" t="n">
-        <v>57876</v>
+        <v>100719</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -875,6 +875,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,46 +894,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128832928</v>
+        <v>128832951</v>
       </c>
       <c r="B4" t="n">
-        <v>100713</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -984,7 +985,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -996,7 +996,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Susanne Hernqvist, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Susanne Hernqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -784,46 +784,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128832928</v>
+        <v>128832951</v>
       </c>
       <c r="B3" t="n">
-        <v>100719</v>
+        <v>57876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -875,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,46 +893,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128832951</v>
+        <v>128832928</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>100726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -985,6 +984,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -784,46 +784,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128832951</v>
+        <v>128832928</v>
       </c>
       <c r="B3" t="n">
-        <v>57876</v>
+        <v>100726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -875,6 +875,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,46 +894,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128832928</v>
+        <v>128832951</v>
       </c>
       <c r="B4" t="n">
-        <v>100726</v>
+        <v>57876</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -984,7 +985,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -784,46 +784,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128832928</v>
+        <v>128832951</v>
       </c>
       <c r="B3" t="n">
-        <v>100726</v>
+        <v>57876</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -875,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,46 +893,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128832951</v>
+        <v>128832928</v>
       </c>
       <c r="B4" t="n">
-        <v>57876</v>
+        <v>100726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -985,6 +984,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128832998</v>
       </c>
       <c r="B2" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128832951</v>
       </c>
       <c r="B3" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128832928</v>
       </c>
       <c r="B4" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128832998</v>
       </c>
       <c r="B2" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128832951</v>
       </c>
       <c r="B3" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128832928</v>
       </c>
       <c r="B4" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>128832928</v>
       </c>
       <c r="B4" t="n">
-        <v>100745</v>
+        <v>100750</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>128832928</v>
       </c>
       <c r="B4" t="n">
-        <v>100750</v>
+        <v>100753</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128832998</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128832951</v>
       </c>
       <c r="B3" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128832928</v>
       </c>
       <c r="B4" t="n">
-        <v>100753</v>
+        <v>100763</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>128832928</v>
       </c>
       <c r="B4" t="n">
-        <v>100763</v>
+        <v>100770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128832998</v>
       </c>
       <c r="B2" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128832951</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>128832928</v>
       </c>
       <c r="B4" t="n">
-        <v>100770</v>
+        <v>100772</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -784,46 +784,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128832951</v>
+        <v>128832928</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>100772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -875,6 +875,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,46 +894,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128832928</v>
+        <v>128832951</v>
       </c>
       <c r="B4" t="n">
-        <v>100772</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -984,7 +985,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -784,46 +784,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128832928</v>
+        <v>128832951</v>
       </c>
       <c r="B3" t="n">
-        <v>100772</v>
+        <v>57887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -875,7 +875,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,46 +893,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128832951</v>
+        <v>128832928</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>100798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -985,6 +984,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -784,46 +784,46 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128832951</v>
+        <v>128832928</v>
       </c>
       <c r="B3" t="n">
-        <v>57887</v>
+        <v>100799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -875,6 +875,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -893,46 +894,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128832928</v>
+        <v>128832951</v>
       </c>
       <c r="B4" t="n">
-        <v>100798</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -984,7 +985,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>128832928</v>
       </c>
       <c r="B3" t="n">
-        <v>100799</v>
+        <v>100800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>130450121</v>
       </c>
       <c r="B5" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>130450121</v>
       </c>
       <c r="B5" t="n">
-        <v>80192</v>
+        <v>80218</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>130450121</v>
       </c>
       <c r="B5" t="n">
-        <v>80218</v>
+        <v>80220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>130450121</v>
       </c>
       <c r="B5" t="n">
-        <v>80220</v>
+        <v>80228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>130450121</v>
       </c>
       <c r="B5" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41312-2025 artfynd.xlsx
+++ b/artfynd/A 41312-2025 artfynd.xlsx
@@ -1006,7 +1006,7 @@
         <v>130450121</v>
       </c>
       <c r="B5" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
